--- a/tame_output/ON/bt/strategyON_20240924.xlsx
+++ b/tame_output/ON/bt/strategyON_20240924.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>43.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.3%</t>
+          <t>420.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.7%</t>
+          <t>-574.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-49.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-60.8%</t>
+          <t>-49.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>135.7%</t>
+          <t>138.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>143.5%</t>
+          <t>150.3%</t>
         </is>
       </c>
     </row>
@@ -48655,10 +48655,10 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.243866992744838</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.890578880896658</v>
       </c>
       <c r="F2048" t="n">
         <v>1.240520115457577</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.418973825321283</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.780788061459546</v>
       </c>
       <c r="F2049" t="n">
         <v>1.240520115457577</v>
@@ -48701,10 +48701,10 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.22287367189076</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.866250741828696</v>
       </c>
       <c r="F2050" t="n">
         <v>1.4366202688881</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-4.069848279777475</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.026631898246914</v>
       </c>
       <c r="F2051" t="n">
         <v>1.589645661001384</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-4.098155593650746</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.202775197605898</v>
       </c>
       <c r="F2052" t="n">
         <v>1.589645661001384</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.264748818764268</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.105540858914572</v>
       </c>
       <c r="F2053" t="n">
         <v>1.423052435887861</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.241713025402702</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.118431578920916</v>
       </c>
       <c r="F2054" t="n">
         <v>1.423052435887861</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.212467044947005</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.12774802622669</v>
       </c>
       <c r="F2055" t="n">
         <v>1.423052435887861</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.319392592824856</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.082271046233185</v>
       </c>
       <c r="F2056" t="n">
         <v>1.31612688801001</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.464411151332105</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.025692424973519</v>
       </c>
       <c r="F2057" t="n">
         <v>1.171108329502762</v>
@@ -48885,10 +48885,10 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.582752917116823</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.078286957917385</v>
       </c>
       <c r="F2058" t="n">
         <v>1.181794368065652</v>
@@ -48908,10 +48908,10 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.634163339437531</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.055508486115041</v>
       </c>
       <c r="F2059" t="n">
         <v>1.181794368065652</v>
@@ -48931,10 +48931,10 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.713582790645282</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.02364383370623</v>
       </c>
       <c r="F2060" t="n">
         <v>1.181794368065652</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.8090457885625</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>1.985452528097386</v>
       </c>
       <c r="F2061" t="n">
         <v>1.181794368065652</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.744669877711785</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.009299289000282</v>
       </c>
       <c r="F2062" t="n">
         <v>1.246170278916367</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.800039039843979</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>1.992885441895131</v>
       </c>
       <c r="F2063" t="n">
         <v>1.246170278916367</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.708604079325242</v>
+        <v>-4.818257506841587</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.028997789445559</v>
+        <v>1.985136418439021</v>
       </c>
       <c r="F2064" t="n">
         <v>1.221063841660525</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.620397245177664</v>
+        <v>-4.730050672694009</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.084154915954909</v>
+        <v>2.04029354494837</v>
       </c>
       <c r="F2065" t="n">
         <v>1.221063841660525</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.514362249972354</v>
+        <v>-4.6240156774887</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.11026961456176</v>
+        <v>2.066408243555222</v>
       </c>
       <c r="F2066" t="n">
         <v>1.221063841660525</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.331150586839259</v>
+        <v>-4.440804014355605</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.185985229279044</v>
+        <v>2.142123858272505</v>
       </c>
       <c r="F2067" t="n">
         <v>1.221063841660525</v>
@@ -49115,10 +49115,10 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.259429139825408</v>
+        <v>-4.369082567341754</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.180464993932474</v>
+        <v>2.136603622925936</v>
       </c>
       <c r="F2068" t="n">
         <v>1.292785288674375</v>
@@ -49138,10 +49138,10 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.237056114217702</v>
+        <v>-4.346709541734048</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.136329950096728</v>
+        <v>2.09246857909019</v>
       </c>
       <c r="F2069" t="n">
         <v>1.304041039787277</v>
@@ -49161,10 +49161,10 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.270072410128447</v>
+        <v>-4.379725837644792</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.308321636617785</v>
+        <v>2.264460265611247</v>
       </c>
       <c r="F2070" t="n">
         <v>1.234603663120525</v>
@@ -49184,10 +49184,10 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.258544774478838</v>
+        <v>-4.368198201995184</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.304853916705878</v>
+        <v>2.26099254569934</v>
       </c>
       <c r="F2071" t="n">
         <v>1.293604321321888</v>
@@ -49207,10 +49207,10 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.355886275821207</v>
+        <v>-4.465539703337552</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.269585428690719</v>
+        <v>2.225724057684181</v>
       </c>
       <c r="F2072" t="n">
         <v>1.249184139156399</v>
@@ -49230,10 +49230,10 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.441742305161173</v>
+        <v>-4.551395732677519</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.236494099147571</v>
+        <v>2.192632728141032</v>
       </c>
       <c r="F2073" t="n">
         <v>1.206808069930264</v>
@@ -49253,10 +49253,10 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.450579102577293</v>
+        <v>-4.560232530093638</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.215378582001625</v>
+        <v>2.171517210995086</v>
       </c>
       <c r="F2074" t="n">
         <v>1.199365897288914</v>
@@ -49276,10 +49276,10 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.541961665142751</v>
+        <v>-4.651615092659097</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.188990068020491</v>
+        <v>2.145128697013952</v>
       </c>
       <c r="F2075" t="n">
         <v>1.162801012569569</v>
@@ -49299,10 +49299,10 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.530254947155745</v>
+        <v>-4.639908374672091</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.295801013039561</v>
+        <v>2.251939642033022</v>
       </c>
       <c r="F2076" t="n">
         <v>1.174507730556575</v>
@@ -49322,10 +49322,10 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.601167020898023</v>
+        <v>-4.710820448414369</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.270468522274054</v>
+        <v>2.226607151267515</v>
       </c>
       <c r="F2077" t="n">
         <v>1.174507730556575</v>
@@ -49345,10 +49345,10 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.611483119064375</v>
+        <v>-4.721136546580721</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.479246916285571</v>
+        <v>2.435385545279033</v>
       </c>
       <c r="F2078" t="n">
         <v>1.174507730556575</v>
@@ -49362,16 +49362,16 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.611389151047002</v>
+        <v>-4.721042578563348</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.47846317040461</v>
+        <v>2.434601799398072</v>
       </c>
       <c r="F2079" t="n">
         <v>1.174877591903893</v>
@@ -49391,10 +49391,10 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.618607975246847</v>
+        <v>-4.728261402763192</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.469807626669026</v>
+        <v>2.425946255662488</v>
       </c>
       <c r="F2080" t="n">
         <v>1.174877591903893</v>
@@ -49408,16 +49408,16 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.617659552128808</v>
+        <v>-4.727312979645154</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.470186995916241</v>
+        <v>2.426325624909703</v>
       </c>
       <c r="F2081" t="n">
         <v>1.174877591903893</v>
@@ -49431,16 +49431,16 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663624</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.774728010384433</v>
+        <v>-4.884381437900778</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.420087220595084</v>
+        <v>2.376225849588546</v>
       </c>
       <c r="F2082" t="n">
         <v>1.174877591903893</v>
@@ -49454,16 +49454,16 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424768</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.768735763595621</v>
+        <v>-4.878389191111967</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.424430117734996</v>
+        <v>2.380568746728458</v>
       </c>
       <c r="F2083" t="n">
         <v>1.174877591903893</v>
@@ -49477,16 +49477,16 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149217</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.680177802464853</v>
+        <v>-4.789831229981199</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.453507438205072</v>
+        <v>2.409646067198534</v>
       </c>
       <c r="F2084" t="n">
         <v>1.174877591903893</v>
@@ -49500,16 +49500,16 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.662418724961779</v>
+        <v>-4.772072152478125</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.459919746645297</v>
+        <v>2.416058375638759</v>
       </c>
       <c r="F2085" t="n">
         <v>1.174877591903893</v>
@@ -49523,16 +49523,16 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720996</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.562788573912711</v>
+        <v>-4.672442001429057</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.512553992973511</v>
+        <v>2.468692621966973</v>
       </c>
       <c r="F2086" t="n">
         <v>1.274507742952961</v>
@@ -49546,16 +49546,16 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.612188082601723</v>
+        <v>-4.721841510118068</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.681948454996633</v>
+        <v>2.638087083990095</v>
       </c>
       <c r="F2087" t="n">
         <v>1.284766576384706</v>
@@ -49569,16 +49569,16 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.405503608959346</v>
+        <v>-4.515157036475692</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.751810917556446</v>
+        <v>2.707949546549908</v>
       </c>
       <c r="F2088" t="n">
         <v>1.491451050027081</v>
@@ -49592,16 +49592,16 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.439660503956873</v>
+        <v>-4.549313931473218</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.74014967321154</v>
+        <v>2.696288302205002</v>
       </c>
       <c r="F2089" t="n">
         <v>1.407867280486269</v>
@@ -49621,10 +49621,10 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.347071024895416</v>
+        <v>-4.456724452411762</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.13068257882579</v>
+        <v>3.086821207819252</v>
       </c>
       <c r="F2090" t="n">
         <v>1.407867280486269</v>
@@ -49644,10 +49644,10 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.406959652718967</v>
+        <v>-4.516613080235312</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.111290239263473</v>
+        <v>3.067428868256935</v>
       </c>
       <c r="F2091" t="n">
         <v>1.393745365798804</v>
@@ -49667,10 +49667,10 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.354743342922625</v>
+        <v>-4.46439677043897</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.182006704505538</v>
+        <v>3.138145333498999</v>
       </c>
       <c r="F2092" t="n">
         <v>1.393745365798804</v>
@@ -49690,10 +49690,10 @@
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.322845825837379</v>
+        <v>-4.432499253353725</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.203579681549646</v>
+        <v>3.159718310543108</v>
       </c>
       <c r="F2093" t="n">
         <v>1.42564288288405</v>
@@ -49713,10 +49713,10 @@
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.33760115003752</v>
+        <v>-4.447254577553865</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.193315135908787</v>
+        <v>3.149453764902249</v>
       </c>
       <c r="F2094" t="n">
         <v>1.42564288288405</v>
@@ -49736,10 +49736,10 @@
         <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.288136526667608</v>
+        <v>-4.397789954183954</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.204025488673032</v>
+        <v>3.160164117666493</v>
       </c>
       <c r="F2095" t="n">
         <v>1.475107506253962</v>
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.68444579116294</v>
+        <v>3.715217304977155</v>
       </c>
       <c r="C2096" t="n">
         <v>4.916044191368758</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.131299560020921</v>
+        <v>-4.126878195495206</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.263167943046641</v>
+        <v>3.264936488856927</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.631944472900648</v>
+        <v>1.746019264942709</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.895210875109147</v>
+        <v>5.963655750334383</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240924.xlsx
+++ b/tame_output/ON/bt/strategyON_20240924.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.9%</t>
+          <t>419.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.3%</t>
+          <t>-588.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-55.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.2%</t>
+          <t>-320.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-66.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>138.2%</t>
+          <t>134.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>150.3%</t>
+          <t>140.2%</t>
         </is>
       </c>
     </row>
@@ -48655,10 +48655,10 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.243866992744838</v>
+        <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.890578880896658</v>
+        <v>1.934440251903196</v>
       </c>
       <c r="F2048" t="n">
         <v>1.240520115457577</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.418973825321283</v>
+        <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.780788061459546</v>
+        <v>1.824649432466085</v>
       </c>
       <c r="F2049" t="n">
         <v>1.240520115457577</v>
@@ -48701,10 +48701,10 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.22287367189076</v>
+        <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.866250741828696</v>
+        <v>1.910112112835234</v>
       </c>
       <c r="F2050" t="n">
         <v>1.4366202688881</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.069848279777475</v>
+        <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.026631898246914</v>
+        <v>2.070493269253452</v>
       </c>
       <c r="F2051" t="n">
         <v>1.589645661001384</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.098155593650746</v>
+        <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.202775197605898</v>
+        <v>2.246636568612437</v>
       </c>
       <c r="F2052" t="n">
         <v>1.589645661001384</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.264748818764268</v>
+        <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.105540858914572</v>
+        <v>2.14940222992111</v>
       </c>
       <c r="F2053" t="n">
         <v>1.423052435887861</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.241713025402702</v>
+        <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.118431578920916</v>
+        <v>2.162292949927454</v>
       </c>
       <c r="F2054" t="n">
         <v>1.423052435887861</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.212467044947005</v>
+        <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.12774802622669</v>
+        <v>2.171609397233228</v>
       </c>
       <c r="F2055" t="n">
         <v>1.423052435887861</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.319392592824856</v>
+        <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.082271046233185</v>
+        <v>2.126132417239723</v>
       </c>
       <c r="F2056" t="n">
         <v>1.31612688801001</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.464411151332105</v>
+        <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.025692424973519</v>
+        <v>2.069553795980058</v>
       </c>
       <c r="F2057" t="n">
         <v>1.171108329502762</v>
@@ -48885,10 +48885,10 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.582752917116823</v>
+        <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.078286957917385</v>
+        <v>2.122148328923924</v>
       </c>
       <c r="F2058" t="n">
         <v>1.181794368065652</v>
@@ -48908,10 +48908,10 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.634163339437531</v>
+        <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.055508486115041</v>
+        <v>2.099369857121579</v>
       </c>
       <c r="F2059" t="n">
         <v>1.181794368065652</v>
@@ -48931,10 +48931,10 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.713582790645282</v>
+        <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.02364383370623</v>
+        <v>2.067505204712768</v>
       </c>
       <c r="F2060" t="n">
         <v>1.181794368065652</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.8090457885625</v>
+        <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.985452528097386</v>
+        <v>2.029313899103924</v>
       </c>
       <c r="F2061" t="n">
         <v>1.181794368065652</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.744669877711785</v>
+        <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.009299289000282</v>
+        <v>2.053160660006821</v>
       </c>
       <c r="F2062" t="n">
         <v>1.246170278916367</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.800039039843979</v>
+        <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.992885441895131</v>
+        <v>2.036746812901669</v>
       </c>
       <c r="F2063" t="n">
         <v>1.246170278916367</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.818257506841587</v>
+        <v>-4.708604079325242</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.985136418439021</v>
+        <v>2.028997789445559</v>
       </c>
       <c r="F2064" t="n">
         <v>1.221063841660525</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.730050672694009</v>
+        <v>-4.620397245177664</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.04029354494837</v>
+        <v>2.084154915954909</v>
       </c>
       <c r="F2065" t="n">
         <v>1.221063841660525</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.6240156774887</v>
+        <v>-4.514362249972354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.066408243555222</v>
+        <v>2.11026961456176</v>
       </c>
       <c r="F2066" t="n">
         <v>1.221063841660525</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.440804014355605</v>
+        <v>-4.331150586839259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.142123858272505</v>
+        <v>2.185985229279044</v>
       </c>
       <c r="F2067" t="n">
         <v>1.221063841660525</v>
@@ -49115,10 +49115,10 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.369082567341754</v>
+        <v>-4.259429139825408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.136603622925936</v>
+        <v>2.180464993932474</v>
       </c>
       <c r="F2068" t="n">
         <v>1.292785288674375</v>
@@ -49138,10 +49138,10 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.346709541734048</v>
+        <v>-4.237056114217702</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.09246857909019</v>
+        <v>2.136329950096728</v>
       </c>
       <c r="F2069" t="n">
         <v>1.304041039787277</v>
@@ -49161,10 +49161,10 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.379725837644792</v>
+        <v>-4.270072410128447</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.264460265611247</v>
+        <v>2.308321636617785</v>
       </c>
       <c r="F2070" t="n">
         <v>1.234603663120525</v>
@@ -49184,10 +49184,10 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.368198201995184</v>
+        <v>-4.258544774478838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.26099254569934</v>
+        <v>2.304853916705878</v>
       </c>
       <c r="F2071" t="n">
         <v>1.293604321321888</v>
@@ -49207,10 +49207,10 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.465539703337552</v>
+        <v>-4.355886275821207</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.225724057684181</v>
+        <v>2.269585428690719</v>
       </c>
       <c r="F2072" t="n">
         <v>1.249184139156399</v>
@@ -49230,10 +49230,10 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.551395732677519</v>
+        <v>-4.441742305161173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.192632728141032</v>
+        <v>2.236494099147571</v>
       </c>
       <c r="F2073" t="n">
         <v>1.206808069930264</v>
@@ -49253,10 +49253,10 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.560232530093638</v>
+        <v>-4.450579102577293</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.171517210995086</v>
+        <v>2.215378582001625</v>
       </c>
       <c r="F2074" t="n">
         <v>1.199365897288914</v>
@@ -49276,10 +49276,10 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.651615092659097</v>
+        <v>-4.541961665142751</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.145128697013952</v>
+        <v>2.188990068020491</v>
       </c>
       <c r="F2075" t="n">
         <v>1.162801012569569</v>
@@ -49299,10 +49299,10 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.639908374672091</v>
+        <v>-4.530254947155745</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.251939642033022</v>
+        <v>2.295801013039561</v>
       </c>
       <c r="F2076" t="n">
         <v>1.174507730556575</v>
@@ -49322,10 +49322,10 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.710820448414369</v>
+        <v>-4.601167020898023</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.226607151267515</v>
+        <v>2.270468522274054</v>
       </c>
       <c r="F2077" t="n">
         <v>1.174507730556575</v>
@@ -49345,10 +49345,10 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.721136546580721</v>
+        <v>-4.611483119064375</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.435385545279033</v>
+        <v>2.479246916285571</v>
       </c>
       <c r="F2078" t="n">
         <v>1.174507730556575</v>
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.721042578563348</v>
+        <v>-4.759997515424409</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.434601799398072</v>
+        <v>2.419019824653647</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.174877591903893</v>
+        <v>1.113688188625291</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.028301810279495</v>
+        <v>4.991588168312334</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.728261402763192</v>
+        <v>-4.767216339624254</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.425946255662488</v>
+        <v>2.410364280918063</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.174877591903893</v>
+        <v>1.113688188625291</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.022533796223849</v>
+        <v>4.985820154256688</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.727312979645154</v>
+        <v>-4.766267916506215</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.426325624909703</v>
+        <v>2.410743650165279</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.174877591903893</v>
+        <v>1.113688188625291</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.022533796223849</v>
+        <v>4.985820154256688</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663624</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.884381437900778</v>
+        <v>-4.923336374761838</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.376225849588546</v>
+        <v>2.360643874844121</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.174877591903893</v>
+        <v>1.113688188625291</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.035261404204941</v>
+        <v>4.99854776223778</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424768</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.878389191111967</v>
+        <v>-4.917344127973027</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.380568746728458</v>
+        <v>2.364986771984034</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.174877591903893</v>
+        <v>1.113688188625291</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.037207402629329</v>
+        <v>5.000493760662168</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149217</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.789831229981199</v>
+        <v>-4.828786166842259</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.409646067198534</v>
+        <v>2.394064092454109</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.174877591903893</v>
+        <v>1.113688188625291</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.030861538647097</v>
+        <v>4.994147896679936</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.73530072138309</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.772072152478125</v>
+        <v>-4.811027089339185</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.416058375638759</v>
+        <v>2.400476400894335</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.174877591903893</v>
+        <v>1.113688188625291</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.030170216086093</v>
+        <v>4.993456574118932</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720996</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.672442001429057</v>
+        <v>-4.711396938290117</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.468692621966973</v>
+        <v>2.453110647222549</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.274507742952961</v>
+        <v>1.213318339674358</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.10273049262412</v>
+        <v>5.066016850656959</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.721841510118068</v>
+        <v>-4.760796446979128</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.638087083990095</v>
+        <v>2.622505109245671</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.284766576384706</v>
+        <v>1.223577173106103</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.298040058181893</v>
+        <v>5.261326416214732</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963131</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.515157036475692</v>
+        <v>-4.554111973336752</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.707949546549908</v>
+        <v>2.692367571805483</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.491451050027081</v>
+        <v>1.430261646748479</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.409239415470181</v>
+        <v>5.372525773503019</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162541</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.549313931473218</v>
+        <v>-4.588268868334278</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.696288302205002</v>
+        <v>2.680706327460578</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.407867280486269</v>
+        <v>1.346677877207666</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.361090667399798</v>
+        <v>5.324377025432637</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.456724452411762</v>
+        <v>-4.495679389272822</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.086821207819252</v>
+        <v>3.071239233074828</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.407867280486269</v>
+        <v>1.346677877207666</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.714587781389466</v>
+        <v>5.677874139422305</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.516613080235312</v>
+        <v>-4.555568017096372</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.067428868256935</v>
+        <v>3.051846893512511</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.393745365798804</v>
+        <v>1.332555962520201</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.710677744144091</v>
+        <v>5.673964102176929</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.46439677043897</v>
+        <v>-4.50335170730003</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.138145333498999</v>
+        <v>3.122563358754575</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.393745365798804</v>
+        <v>1.332555962520201</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.760507685467618</v>
+        <v>5.723794043500456</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.432499253353725</v>
+        <v>-4.471454190214785</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.159718310543108</v>
+        <v>3.144136335798684</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.42564288288405</v>
+        <v>1.364453479605447</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.788460165928776</v>
+        <v>5.751746523961615</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.447254577553865</v>
+        <v>-4.486209514414925</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.149453764902249</v>
+        <v>3.133871790157825</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.42564288288405</v>
+        <v>1.364453479605447</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.784097749967973</v>
+        <v>5.747384108000812</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.397789954183954</v>
+        <v>-4.436744891045014</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.160164117666493</v>
+        <v>3.14458214292207</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.475107506253962</v>
+        <v>1.413918102975359</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.804701027406201</v>
+        <v>5.767987385439039</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.715217304977155</v>
+        <v>3.683577935241008</v>
       </c>
       <c r="C2096" t="n">
         <v>4.916044191368758</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.126878195495206</v>
+        <v>-4.273636898891398</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.264936488856927</v>
+        <v>3.20623300749845</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.746019264942709</v>
+        <v>1.577026095128974</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.963655750334383</v>
+        <v>5.862259848446143</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240924.xlsx
+++ b/tame_output/ON/bt/strategyON_20240924.xlsx
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
@@ -49730,7 +49730,7 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135747</v>
+        <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
         <v>4.919636523653823</v>
@@ -49753,7 +49753,7 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.683577935241008</v>
+        <v>3.683577935241006</v>
       </c>
       <c r="C2096" t="n">
         <v>4.916044191368758</v>

--- a/tame_output/ON/bt/strategyON_20240924.xlsx
+++ b/tame_output/ON/bt/strategyON_20240924.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.3%</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.2%</t>
+          <t>420.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.9%</t>
+          <t>-574.6%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-49.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.1%</t>
+          <t>-320.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-60.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>134.5%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>141.1%</t>
+          <t>144.8%</t>
         </is>
       </c>
     </row>
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.759997515424409</v>
+        <v>-4.611389151047002</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.419019824653647</v>
+        <v>2.47846317040461</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.113688188625291</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.991588168312334</v>
+        <v>5.028301810279495</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.767216339624254</v>
+        <v>-4.759755378703147</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.410364280918063</v>
+        <v>2.413348665286506</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.113688188625291</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.985820154256688</v>
+        <v>5.022533796223849</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.766267916506215</v>
+        <v>-4.758806955585109</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.410743650165279</v>
+        <v>2.413728034533722</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.113688188625291</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.985820154256688</v>
+        <v>5.022533796223849</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.923336374761838</v>
+        <v>-4.915875413840732</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.360643874844121</v>
+        <v>2.363628259212564</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.113688188625291</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.99854776223778</v>
+        <v>5.035261404204941</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.917344127973027</v>
+        <v>-4.909883167051921</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.364986771984034</v>
+        <v>2.367971156352477</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.113688188625291</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.000493760662168</v>
+        <v>5.037207402629329</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.828786166842259</v>
+        <v>-4.821325205921153</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.394064092454109</v>
+        <v>2.397048476822552</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.113688188625291</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.994147896679936</v>
+        <v>5.030861538647097</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.811027089339185</v>
+        <v>-4.803566128418079</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.400476400894335</v>
+        <v>2.403460785262777</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.113688188625291</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.993456574118932</v>
+        <v>5.030170216086093</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.711396938290117</v>
+        <v>-4.703935977369011</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.453110647222549</v>
+        <v>2.456095031590992</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.213318339674358</v>
+        <v>1.274507742952961</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.066016850656959</v>
+        <v>5.10273049262412</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.760796446979128</v>
+        <v>-4.753335486058022</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.622505109245671</v>
+        <v>2.625489493614113</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.223577173106103</v>
+        <v>1.284766576384706</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.261326416214732</v>
+        <v>5.298040058181893</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.554111973336752</v>
+        <v>-4.546651012415646</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.692367571805483</v>
+        <v>2.695351956173926</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.430261646748479</v>
+        <v>1.491451050027081</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.372525773503019</v>
+        <v>5.409239415470181</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.588268868334278</v>
+        <v>-4.580807907413172</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.680706327460578</v>
+        <v>2.68369071182902</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.346677877207666</v>
+        <v>1.407867280486269</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.324377025432637</v>
+        <v>5.361090667399798</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.495679389272822</v>
+        <v>-4.488218428351716</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.071239233074828</v>
+        <v>3.074223617443271</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.346677877207666</v>
+        <v>1.407867280486269</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.677874139422305</v>
+        <v>5.714587781389466</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.555568017096372</v>
+        <v>-4.548107056175266</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.051846893512511</v>
+        <v>3.054831277880953</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.332555962520201</v>
+        <v>1.393745365798804</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.673964102176929</v>
+        <v>5.710677744144091</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.50335170730003</v>
+        <v>-4.495890746378924</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.122563358754575</v>
+        <v>3.125547743123017</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.332555962520201</v>
+        <v>1.393745365798804</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.723794043500456</v>
+        <v>5.760507685467618</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.471454190214785</v>
+        <v>-4.463993229293679</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.144136335798684</v>
+        <v>3.147120720167127</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.364453479605447</v>
+        <v>1.42564288288405</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.751746523961615</v>
+        <v>5.788460165928776</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.486209514414925</v>
+        <v>-4.478748553493819</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.133871790157825</v>
+        <v>3.136856174526268</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.364453479605447</v>
+        <v>1.42564288288405</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.747384108000812</v>
+        <v>5.784097749967973</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.436744891045014</v>
+        <v>-4.429283930123908</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.14458214292207</v>
+        <v>3.147566527290512</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.413918102975359</v>
+        <v>1.475107506253962</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.767987385439039</v>
+        <v>5.804701027406201</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479221</v>
+        <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
         <v>4.916044191368758</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.273636898891398</v>
+        <v>-4.266175937970292</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.20623300749845</v>
+        <v>3.209217391866892</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.577026095128974</v>
+        <v>1.638215498407577</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.862259848446143</v>
+        <v>5.898973490413304</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.680804128279053</v>
+        <v>3.683939068533957</v>
       </c>
       <c r="C2097" t="n">
         <v>4.925091228059886</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.133139326342866</v>
+        <v>-4.130259518721763</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.271479073208991</v>
+        <v>3.272630996257432</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.577026095128974</v>
+        <v>1.638215498407577</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.871306885137271</v>
+        <v>5.908020527104432</v>
       </c>
     </row>
   </sheetData>
